--- a/scorecard/Praedium_Development_Review_PRIVATE.xlsx
+++ b/scorecard/Praedium_Development_Review_PRIVATE.xlsx
@@ -551,37 +551,37 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Agent 1 (type name)</t>
+          <t>Gabrielle Gillie</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Agent 2 (type name)</t>
+          <t>Dillon</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Agent 3 (type name)</t>
+          <t>Marcus Lominick</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Agent 4 (type name)</t>
+          <t>Mary Elizabeth Young</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Agent 5 (type name)</t>
+          <t>Jayan Abraham</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Agent 6 (type name)</t>
+          <t>Agent 6</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Agent 7 (type name)</t>
+          <t>Agent 7</t>
         </is>
       </c>
     </row>

--- a/scorecard/Praedium_Development_Review_PRIVATE.xlsx
+++ b/scorecard/Praedium_Development_Review_PRIVATE.xlsx
@@ -576,7 +576,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Agent 6</t>
+          <t>Nicholas Carnes</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
